--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22923,7 +22923,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -23473,7 +23473,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -28547,7 +28547,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29647,7 +29647,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -29799,16 +29799,16 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O163" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>0.6794701866111612</v>
+        <v>0.6941614338892403</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -32627,7 +32627,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -33177,7 +33177,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33727,7 +33727,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33879,16 +33879,16 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O185" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>0.07712904820991559</v>
+        <v>0.08814748366847497</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7208</v>
+        <v>7215</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -26515,16 +26515,16 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O143" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.6317236329574039</v>
+        <v>0.6353964447769237</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -31287,16 +31287,16 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O169" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>0.7088526811673195</v>
+        <v>0.7051798693477997</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -35367,16 +35367,16 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O191" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q191" t="n">
         <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>0.09182029548799475</v>
+        <v>0.1212027900441531</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -36455,16 +36455,16 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36617,10 +36617,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -36929,6 +36929,408 @@
       <c r="BC199" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="n">
+        <v>1</v>
+      </c>
+      <c r="P200" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
+      </c>
+      <c r="O201" t="n">
+        <v>1</v>
+      </c>
+      <c r="P201" t="n">
+        <v>1</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36965,7 +37367,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -37048,7 +37450,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -37058,7 +37460,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -37078,7 +37480,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -37110,7 +37512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7222</v>
+        <v>7232</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>46</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>19</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -2146,9 +2131,6 @@
       <c r="O10" t="n">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.2122770990954608</v>
       </c>
@@ -2791,7 +2773,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2920,6 @@
       <c r="O14" t="n">
         <v>118</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>1.102695890537435</v>
       </c>
@@ -3647,9 +3626,6 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3899,7 +3875,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4197,9 +4173,6 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4449,7 +4422,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -4747,9 +4720,6 @@
       <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -4999,7 +4969,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5297,9 +5267,6 @@
       <c r="P27" t="n">
         <v>5</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -5549,7 +5516,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5992,9 +5959,6 @@
       <c r="O31" t="n">
         <v>19</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6385,9 +6349,6 @@
       <c r="O33" t="n">
         <v>15</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -6533,9 +6494,6 @@
       <c r="O34" t="n">
         <v>7</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -6929,9 +6887,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -7080,9 +7035,6 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7332,7 +7284,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -7479,9 +7431,6 @@
       <c r="O39" t="n">
         <v>3</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -7627,9 +7576,6 @@
       <c r="O40" t="n">
         <v>12</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.2122770990954608</v>
       </c>
@@ -8272,7 +8218,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8419,9 +8365,6 @@
       <c r="O44" t="n">
         <v>90</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.8410392385455011</v>
       </c>
@@ -9128,9 +9071,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9380,7 +9320,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9678,9 +9618,6 @@
       <c r="P51" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -9930,7 +9867,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10228,9 +10165,6 @@
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -10480,7 +10414,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10923,9 +10857,6 @@
       <c r="O58" t="n">
         <v>33</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11316,9 +11247,6 @@
       <c r="O60" t="n">
         <v>19</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.2109283534111222</v>
       </c>
@@ -11464,9 +11392,6 @@
       <c r="O61" t="n">
         <v>5</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -11860,9 +11785,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12011,9 +11933,6 @@
       <c r="P64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12263,7 +12182,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -12410,9 +12329,6 @@
       <c r="O66" t="n">
         <v>5</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.009689849618960231</v>
       </c>
@@ -12558,9 +12474,6 @@
       <c r="O67" t="n">
         <v>15</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -13203,7 +13116,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -13350,9 +13263,6 @@
       <c r="O71" t="n">
         <v>96</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.8971085211152012</v>
       </c>
@@ -14059,9 +13969,6 @@
       <c r="P75" t="n">
         <v>3</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -14311,7 +14218,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -14609,9 +14516,6 @@
       <c r="P78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -14861,7 +14765,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15159,9 +15063,6 @@
       <c r="P81" t="n">
         <v>5</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -15411,7 +15312,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15709,9 +15610,6 @@
       <c r="P84" t="n">
         <v>4</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -15961,7 +15859,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -16108,9 +16006,6 @@
       <c r="O86" t="n">
         <v>255</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.9365670139775465</v>
       </c>
@@ -16256,9 +16151,6 @@
       <c r="O87" t="n">
         <v>25</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="S87" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16649,9 +16541,6 @@
       <c r="O89" t="n">
         <v>17</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -16797,9 +16686,6 @@
       <c r="O90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -17193,9 +17079,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -17341,9 +17224,6 @@
       <c r="O93" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -17489,9 +17369,6 @@
       <c r="O94" t="n">
         <v>6</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -17885,9 +17762,6 @@
       <c r="O96" t="n">
         <v>7</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -18134,7 +18008,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -18281,9 +18155,6 @@
       <c r="O98" t="n">
         <v>76</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.7102109125495343</v>
       </c>
@@ -18677,9 +18548,6 @@
       <c r="O100" t="n">
         <v>10</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.04345692446436896</v>
       </c>
@@ -18990,9 +18858,6 @@
       <c r="P102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19242,7 +19107,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -19540,9 +19405,6 @@
       <c r="P105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -19792,7 +19654,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -20090,9 +19952,6 @@
       <c r="P108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -20342,7 +20201,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -20640,9 +20499,6 @@
       <c r="P111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -20892,7 +20748,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -21039,9 +20895,6 @@
       <c r="O113" t="n">
         <v>207</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.7602720466405966</v>
       </c>
@@ -21187,9 +21040,6 @@
       <c r="O114" t="n">
         <v>24</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21580,9 +21430,6 @@
       <c r="O116" t="n">
         <v>18</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -21728,9 +21575,6 @@
       <c r="O117" t="n">
         <v>2</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -22124,9 +21968,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -22272,9 +22113,6 @@
       <c r="O120" t="n">
         <v>3</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -22420,9 +22258,6 @@
       <c r="O121" t="n">
         <v>13</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.2299668573534158</v>
       </c>
@@ -22816,9 +22651,6 @@
       <c r="O123" t="n">
         <v>7</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -23065,7 +22897,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -23212,9 +23044,6 @@
       <c r="O125" t="n">
         <v>38</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.3551054562747671</v>
       </c>
@@ -23608,9 +23437,6 @@
       <c r="O127" t="n">
         <v>14</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.06083969425011655</v>
       </c>
@@ -23921,9 +23747,6 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -24173,7 +23996,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -24471,9 +24294,6 @@
       <c r="P132" t="n">
         <v>2</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -24723,7 +24543,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -25021,9 +24841,6 @@
       <c r="P135" t="n">
         <v>3</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -25273,7 +25090,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -25571,9 +25388,6 @@
       <c r="P138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -25823,7 +25637,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -25970,9 +25784,6 @@
       <c r="O140" t="n">
         <v>97</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.02779086988786304</v>
       </c>
@@ -26121,9 +25932,6 @@
       <c r="P141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -26373,7 +26181,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -26520,9 +26328,6 @@
       <c r="O143" t="n">
         <v>173</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.6353964447769237</v>
       </c>
@@ -26668,9 +26473,6 @@
       <c r="O144" t="n">
         <v>22</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.2442328302655099</v>
       </c>
@@ -26816,9 +26618,6 @@
       <c r="O145" t="n">
         <v>3</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -27212,9 +27011,6 @@
       <c r="O147" t="n">
         <v>2</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -27360,9 +27156,6 @@
       <c r="O148" t="n">
         <v>4</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -27508,9 +27301,6 @@
       <c r="O149" t="n">
         <v>4</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -27904,9 +27694,6 @@
       <c r="O151" t="n">
         <v>7</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.132388232653028</v>
       </c>
@@ -28153,7 +27940,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -28300,9 +28087,6 @@
       <c r="O153" t="n">
         <v>39</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.3644503367030505</v>
       </c>
@@ -28696,9 +28480,6 @@
       <c r="O155" t="n">
         <v>11</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.04780261691080586</v>
       </c>
@@ -28945,7 +28726,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -29092,9 +28873,6 @@
       <c r="O157" t="n">
         <v>165</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.04727312919069485</v>
       </c>
@@ -29243,9 +29021,6 @@
       <c r="P158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -29495,7 +29270,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -29642,9 +29417,6 @@
       <c r="O160" t="n">
         <v>137</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.03925102241894058</v>
       </c>
@@ -29793,9 +29565,6 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -30045,7 +29814,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -30192,9 +29961,6 @@
       <c r="O163" t="n">
         <v>145</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.04154305292515609</v>
       </c>
@@ -30343,9 +30109,6 @@
       <c r="P164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -30595,7 +30358,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -30742,9 +30505,6 @@
       <c r="O166" t="n">
         <v>172</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.04927865588363343</v>
       </c>
@@ -30893,9 +30653,6 @@
       <c r="P167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -31145,7 +30902,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -31292,9 +31049,6 @@
       <c r="O169" t="n">
         <v>192</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.7051798693477997</v>
       </c>
@@ -31440,9 +31194,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -31836,9 +31587,6 @@
       <c r="O172" t="n">
         <v>4</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -31979,16 +31727,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O173" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R173" t="n">
-        <v>0.283036132127281</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -32141,10 +31886,10 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O174" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -32380,9 +32125,6 @@
       <c r="O175" t="n">
         <v>76</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.7102109125495343</v>
       </c>
@@ -32776,9 +32518,6 @@
       <c r="O177" t="n">
         <v>20</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.08691384892873792</v>
       </c>
@@ -33025,7 +32764,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -33172,9 +32911,6 @@
       <c r="O179" t="n">
         <v>136</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.03896451860566364</v>
       </c>
@@ -33323,9 +33059,6 @@
       <c r="P180" t="n">
         <v>1</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -33575,7 +33308,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -33722,9 +33455,6 @@
       <c r="O182" t="n">
         <v>165</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.04727312919069485</v>
       </c>
@@ -33873,9 +33603,6 @@
       <c r="P183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -34125,7 +33852,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -34272,9 +33999,6 @@
       <c r="O185" t="n">
         <v>224</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.06417685417403424</v>
       </c>
@@ -34423,9 +34147,6 @@
       <c r="P186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -34675,7 +34396,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -34822,9 +34543,6 @@
       <c r="O188" t="n">
         <v>234</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.06704189230680362</v>
       </c>
@@ -34973,9 +34691,6 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -35225,7 +34940,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -35372,9 +35087,6 @@
       <c r="O191" t="n">
         <v>33</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.1212027900441531</v>
       </c>
@@ -35520,9 +35232,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -35916,9 +35625,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -36059,16 +35765,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -36221,10 +35924,10 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
@@ -36455,16 +36158,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O197" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R197" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36617,10 +36317,10 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
@@ -36709,7 +36409,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -36856,9 +36556,6 @@
       <c r="O199" t="n">
         <v>226</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.0647498618005881</v>
       </c>
@@ -37007,9 +36704,6 @@
       <c r="P200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -37259,7 +36953,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -37331,6 +37025,151 @@
       <c r="BC201" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>232</v>
+      </c>
+      <c r="O202" t="n">
+        <v>232</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0.06646888468024974</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37367,7 +37206,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -37450,7 +37289,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -37460,7 +37299,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -37512,7 +37351,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7232</v>
+        <v>7470</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -26468,13 +26468,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O144" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R144" t="n">
-        <v>0.2442328302655099</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -31150,12 +31150,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -31189,95 +31189,81 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O170" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R170" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.2442328302655099</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -31304,7 +31290,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -31353,98 +31339,23 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
+      <c r="R171" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -31538,17 +31449,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -31582,81 +31493,170 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>4</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31688,12 +31688,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -31727,95 +31727,81 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O173" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R173" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31842,7 +31828,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -31891,98 +31877,23 @@
       <c r="O174" t="n">
         <v>18</v>
       </c>
+      <c r="R174" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN174" t="b">
-        <v>1</v>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
@@ -32076,17 +31987,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -32120,22 +32031,39 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="O175" t="n">
-        <v>76</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0.7102109125495343</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -32143,6 +32071,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32160,7 +32146,7 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT175" t="n">
@@ -32173,42 +32159,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32235,7 +32221,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -32284,98 +32270,23 @@
       <c r="O176" t="n">
         <v>76</v>
       </c>
+      <c r="R176" t="n">
+        <v>0.7102109125495343</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>Shigellainfektion</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN176" t="b">
-        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
@@ -32469,17 +32380,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -32513,22 +32424,39 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O177" t="n">
-        <v>20</v>
-      </c>
-      <c r="R177" t="n">
-        <v>0.08691384892873792</v>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>76</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Shigellainfektion</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -32536,9 +32464,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN177" t="b">
+        <v>1</v>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
@@ -32548,12 +32534,12 @@
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT177" t="n">
@@ -32561,47 +32547,47 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32614,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -32677,98 +32663,23 @@
       <c r="O178" t="n">
         <v>20</v>
       </c>
+      <c r="R178" t="n">
+        <v>0.08691384892873792</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -32862,17 +32773,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -32897,7 +32808,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -32906,81 +32817,170 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="O179" t="n">
-        <v>136</v>
-      </c>
-      <c r="R179" t="n">
-        <v>0.03896451860566364</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33012,12 +33012,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -33051,98 +33051,81 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O180" t="n">
-        <v>1</v>
-      </c>
-      <c r="P180" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="R180" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.03896451860566364</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33169,7 +33152,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -33221,98 +33204,23 @@
       <c r="P181" t="n">
         <v>1</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -33406,17 +33314,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33441,7 +33349,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -33450,81 +33358,173 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="O182" t="n">
-        <v>165</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0.04727312919069485</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P182" t="n">
+        <v>1</v>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33556,12 +33556,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -33595,98 +33595,81 @@
         </is>
       </c>
       <c r="N183" t="n">
+        <v>165</v>
+      </c>
+      <c r="O183" t="n">
+        <v>165</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.04727312919069485</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="n">
         <v>0</v>
       </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT183" t="n">
-        <v>1</v>
-      </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33713,7 +33696,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -33765,98 +33748,23 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
@@ -33950,17 +33858,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -33985,7 +33893,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -33994,81 +33902,173 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>224</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0.06417685417403424</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34100,12 +34100,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -34130,7 +34130,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -34139,98 +34139,81 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="O186" t="n">
-        <v>1</v>
-      </c>
-      <c r="P186" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="R186" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.06417685417403424</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34257,7 +34240,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -34309,98 +34292,23 @@
       <c r="P187" t="n">
         <v>1</v>
       </c>
+      <c r="R187" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U187" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
@@ -34494,17 +34402,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34529,7 +34437,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34538,81 +34446,173 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="O188" t="n">
-        <v>234</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0.06704189230680362</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P188" t="n">
+        <v>1</v>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN188" t="b">
+        <v>1</v>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34644,12 +34644,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -34683,98 +34683,81 @@
         </is>
       </c>
       <c r="N189" t="n">
+        <v>234</v>
+      </c>
+      <c r="O189" t="n">
+        <v>234</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.06704189230680362</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="n">
         <v>0</v>
       </c>
-      <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP189" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT189" t="n">
-        <v>1</v>
-      </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34801,7 +34784,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -34853,98 +34836,23 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
@@ -35038,17 +34946,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35073,90 +34981,182 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>33</v>
-      </c>
-      <c r="R191" t="n">
-        <v>0.1212027900441531</v>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35188,12 +35188,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -35227,95 +35227,81 @@
         </is>
       </c>
       <c r="N192" t="n">
+        <v>33</v>
+      </c>
+      <c r="O192" t="n">
+        <v>33</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.1212027900441531</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
         <v>0</v>
       </c>
-      <c r="O192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT192" t="n">
-        <v>1</v>
-      </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -35342,7 +35328,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -35391,98 +35377,23 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -35576,17 +35487,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35625,76 +35536,165 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -35726,12 +35726,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35765,95 +35765,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0.05306927477386519</v>
+        <v>0</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35880,7 +35866,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -35929,98 +35915,23 @@
       <c r="O196" t="n">
         <v>3</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -36114,17 +36025,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36163,17 +36074,34 @@
       <c r="O197" t="n">
         <v>3</v>
       </c>
-      <c r="R197" t="n">
-        <v>0.01303707733931069</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -36181,9 +36109,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
@@ -36193,12 +36179,12 @@
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -36206,47 +36192,47 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36273,7 +36259,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36322,98 +36308,23 @@
       <c r="O198" t="n">
         <v>3</v>
       </c>
+      <c r="R198" t="n">
+        <v>0.01303707733931069</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -36507,17 +36418,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36551,81 +36462,170 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
-        <v>226</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.0647498618005881</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36657,12 +36657,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36687,7 +36687,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -36696,98 +36696,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O200" t="n">
-        <v>1</v>
-      </c>
-      <c r="P200" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="R200" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36814,7 +36797,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -36866,98 +36849,23 @@
       <c r="P201" t="n">
         <v>1</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37051,123 +36959,360 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>1</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1</v>
+      </c>
+      <c r="P202" t="n">
+        <v>1</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
         <is>
           <t>志贺菌病</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K203" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N202" t="n">
+      <c r="N203" t="n">
         <v>232</v>
       </c>
-      <c r="O202" t="n">
+      <c r="O203" t="n">
         <v>232</v>
       </c>
-      <c r="R202" t="n">
+      <c r="R203" t="n">
         <v>0.06646888468024974</v>
       </c>
-      <c r="S202" t="inlineStr">
+      <c r="S203" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO202" t="inlineStr">
+      <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP202" t="inlineStr">
+      <c r="AP203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR202" t="inlineStr">
+      <c r="AR203" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS202" t="inlineStr"/>
-      <c r="AT202" t="n">
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="n">
         <v>0</v>
       </c>
-      <c r="AU202" t="inlineStr">
+      <c r="AU203" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV202" t="inlineStr">
+      <c r="AV203" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW202" t="inlineStr">
+      <c r="AW203" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX202" t="inlineStr">
+      <c r="AX203" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY202" t="inlineStr">
+      <c r="AY203" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ202" t="inlineStr">
+      <c r="AZ203" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA202" t="inlineStr">
+      <c r="BA203" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB202" t="inlineStr">
+      <c r="BB203" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC202" t="inlineStr">
+      <c r="BC203" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -37289,7 +37434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -37299,7 +37444,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -37351,7 +37496,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7470</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -36303,13 +36303,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R198" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -36462,10 +36462,10 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7493</v>
+        <v>7494</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -31044,13 +31044,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O169" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R169" t="n">
-        <v>0.7051798693477997</v>
+        <v>0.7125254929868393</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -31334,13 +31334,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R171" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -31493,10 +31493,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -35227,13 +35227,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="O192" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R192" t="n">
-        <v>0.1212027900441531</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7494</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -27541,13 +27541,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R150" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O171" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R171" t="n">
-        <v>0.7125254929868393</v>
+        <v>0.716198304806359</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="O194" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R194" t="n">
-        <v>0.2240415209907072</v>
+        <v>0.2350599564492666</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -37705,6 +37705,405 @@
       <c r="BC205" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="n">
+        <v>1</v>
+      </c>
+      <c r="P206" t="n">
+        <v>1</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA206" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>1</v>
+      </c>
+      <c r="O207" t="n">
+        <v>1</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA207" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37741,7 +38140,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -37824,7 +38223,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -37834,7 +38233,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -37854,7 +38253,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -37886,7 +38285,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7551</v>
+        <v>7557</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="O194" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="R194" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.3268802519372613</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38104,6 +38104,151 @@
       <c r="BC207" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>225</v>
+      </c>
+      <c r="O208" t="n">
+        <v>225</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.06446335798731118</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38140,7 +38285,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -38223,7 +38368,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -38233,7 +38378,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -38285,7 +38430,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7557</v>
+        <v>7807</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -26323,13 +26323,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O143" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R143" t="n">
-        <v>0.6353964447769237</v>
+        <v>0.6390692565964434</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O171" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R171" t="n">
-        <v>0.716198304806359</v>
+        <v>0.7198711166258789</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="O194" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="R194" t="n">
-        <v>0.3268802519372613</v>
+        <v>0.34891712285438</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7807</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="O194" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R194" t="n">
-        <v>0.34891712285438</v>
+        <v>0.3709539937714988</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7815</v>
+        <v>7821</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O194" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R194" t="n">
-        <v>0.3709539937714988</v>
+        <v>0.3746268055910186</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7821</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O171" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R171" t="n">
-        <v>0.7198711166258789</v>
+        <v>0.7272167402649184</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -35617,13 +35617,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="O194" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R194" t="n">
-        <v>0.3746268055910186</v>
+        <v>0.3929908646886175</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7822</v>
+        <v>7829</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -28079,13 +28079,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R153" t="n">
-        <v>0.132388232653028</v>
+        <v>0.1134756279883097</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -28238,10 +28238,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O154" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -31434,13 +31434,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O171" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R171" t="n">
-        <v>0.7272167402649184</v>
+        <v>0.734562363903958</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -32616,12 +32616,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32655,13 +32655,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="R178" t="n">
-        <v>0.7102109125495343</v>
+        <v>0.1891260466471829</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -32695,7 +32695,7 @@
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -32708,42 +32708,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32775,12 +32775,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -32814,29 +32814,29 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>Shigellainfektion</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -32896,17 +32896,17 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -32929,7 +32929,7 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -32942,42 +32942,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33009,12 +33009,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O180" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="R180" t="n">
-        <v>0.08691384892873792</v>
+        <v>0.7102109125495343</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -33073,7 +33073,7 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
@@ -33083,12 +33083,12 @@
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -33096,47 +33096,47 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33168,12 +33168,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33207,29 +33207,29 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O181" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>桿菌性痢疾</t>
+          <t>Shigellainfektion</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
@@ -33239,7 +33239,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -33254,7 +33254,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -33289,17 +33289,17 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>TW_NIDSS_004_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -33307,7 +33307,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
@@ -33317,12 +33317,12 @@
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT181" t="n">
@@ -33330,47 +33330,47 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33402,12 +33402,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -33441,81 +33441,95 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="O182" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="R182" t="n">
-        <v>0.03896451860566364</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33542,17 +33556,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -33577,7 +33591,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -33586,35 +33600,107 @@
         </is>
       </c>
       <c r="N183" t="n">
+        <v>20</v>
+      </c>
+      <c r="O183" t="n">
+        <v>20</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
         <v>1</v>
       </c>
-      <c r="O183" t="n">
-        <v>1</v>
-      </c>
-      <c r="P183" t="n">
-        <v>1</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
@@ -33624,12 +33710,12 @@
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -33637,47 +33723,47 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33704,17 +33790,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33739,7 +33825,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -33748,173 +33834,81 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
-      </c>
-      <c r="P184" t="n">
-        <v>1</v>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN184" t="b">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0.03896451860566364</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -33946,12 +33940,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -33976,7 +33970,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -33985,81 +33979,98 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="O185" t="n">
-        <v>165</v>
+        <v>1</v>
+      </c>
+      <c r="P185" t="n">
+        <v>1</v>
       </c>
       <c r="R185" t="n">
-        <v>0.04727312919069485</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34097,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -34121,7 +34132,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -34130,31 +34141,106 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -34248,17 +34334,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34283,7 +34369,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -34292,173 +34378,81 @@
         </is>
       </c>
       <c r="N187" t="n">
+        <v>165</v>
+      </c>
+      <c r="O187" t="n">
+        <v>165</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0.04727312919069485</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="n">
         <v>0</v>
       </c>
-      <c r="O187" t="n">
-        <v>0</v>
-      </c>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN187" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT187" t="n">
-        <v>1</v>
-      </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34490,12 +34484,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34520,7 +34514,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34529,81 +34523,98 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>224</v>
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>0.06417685417403424</v>
+        <v>0</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34630,7 +34641,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -34665,7 +34676,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -34674,31 +34685,106 @@
         </is>
       </c>
       <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN189" t="b">
         <v>1</v>
-      </c>
-      <c r="O189" t="n">
-        <v>1</v>
-      </c>
-      <c r="P189" t="n">
-        <v>1</v>
-      </c>
-      <c r="R189" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -34792,17 +34878,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34827,7 +34913,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -34836,173 +34922,81 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
-      </c>
-      <c r="P190" t="n">
-        <v>1</v>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN190" t="b">
-        <v>1</v>
+        <v>224</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.06417685417403424</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35034,12 +35028,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35064,7 +35058,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -35073,81 +35067,98 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="O191" t="n">
-        <v>234</v>
+        <v>1</v>
+      </c>
+      <c r="P191" t="n">
+        <v>1</v>
       </c>
       <c r="R191" t="n">
-        <v>0.06704189230680362</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35174,7 +35185,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -35209,7 +35220,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -35218,31 +35229,106 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35336,17 +35422,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35371,7 +35457,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35380,173 +35466,81 @@
         </is>
       </c>
       <c r="N193" t="n">
+        <v>234</v>
+      </c>
+      <c r="O193" t="n">
+        <v>234</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0.06704189230680362</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
+      <c r="AT193" t="n">
         <v>0</v>
       </c>
-      <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP193" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT193" t="n">
-        <v>1</v>
-      </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35578,12 +35572,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35608,90 +35602,107 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N194" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>107</v>
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.3929908646886175</v>
+        <v>0</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35718,17 +35729,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -35753,12 +35764,12 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N195" t="n">
@@ -35767,23 +35778,101 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="n">
+      <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -35797,12 +35886,12 @@
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1210</t>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -35810,47 +35899,47 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35877,17 +35966,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -35921,170 +36010,81 @@
         </is>
       </c>
       <c r="N196" t="n">
+        <v>131</v>
+      </c>
+      <c r="O196" t="n">
+        <v>131</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0.4811383483570925</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="n">
         <v>0</v>
       </c>
-      <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT196" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV196" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36116,12 +36116,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36168,68 +36168,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36256,17 +36270,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -36300,22 +36314,39 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -36323,6 +36354,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN198" t="b">
+        <v>1</v>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -36335,12 +36424,12 @@
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -36348,47 +36437,47 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36415,17 +36504,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36459,170 +36548,81 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O199" t="n">
-        <v>3</v>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
         <v>1</v>
       </c>
+      <c r="R199" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36654,12 +36654,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36693,13 +36693,13 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O200" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R200" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -36718,7 +36718,7 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
@@ -36728,12 +36728,12 @@
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -36741,47 +36741,47 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -36813,12 +36813,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -36852,29 +36852,29 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O201" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="V201" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>桿菌性痢疾</t>
+          <t>Shigellose</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
@@ -36884,7 +36884,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -36899,7 +36899,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -36934,17 +36934,17 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>TW_NIDSS_004_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -36952,7 +36952,7 @@
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
@@ -36962,12 +36962,12 @@
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -36975,47 +36975,47 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37047,12 +37047,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37086,81 +37086,95 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="O202" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="R202" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37187,17 +37201,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -37222,7 +37236,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -37231,35 +37245,107 @@
         </is>
       </c>
       <c r="N203" t="n">
+        <v>4</v>
+      </c>
+      <c r="O203" t="n">
+        <v>4</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
         <v>1</v>
       </c>
-      <c r="O203" t="n">
-        <v>1</v>
-      </c>
-      <c r="P203" t="n">
-        <v>1</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
@@ -37269,12 +37355,12 @@
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+          <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
       <c r="AT203" t="n">
@@ -37282,47 +37368,47 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37349,17 +37435,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37384,7 +37470,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -37393,173 +37479,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
-      </c>
-      <c r="P204" t="n">
-        <v>1</v>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
+        <v>226</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0.0647498618005881</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37591,12 +37585,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37621,7 +37615,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -37630,81 +37624,98 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>232</v>
+        <v>1</v>
+      </c>
+      <c r="P205" t="n">
+        <v>1</v>
       </c>
       <c r="R205" t="n">
-        <v>0.06646888468024974</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37731,7 +37742,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -37766,7 +37777,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -37783,23 +37794,98 @@
       <c r="P206" t="n">
         <v>1</v>
       </c>
-      <c r="R206" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -37893,17 +37979,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37928,7 +38014,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37937,173 +38023,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
-      </c>
-      <c r="P207" t="n">
-        <v>1</v>
-      </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>1</v>
+        <v>232</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.06646888468024974</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38135,120 +38129,918 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="n">
+        <v>1</v>
+      </c>
+      <c r="P208" t="n">
+        <v>1</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA208" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" t="n">
+        <v>1</v>
+      </c>
+      <c r="P209" t="n">
+        <v>1</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA209" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
         <is>
           <t>志贺菌病</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N208" t="n">
+      <c r="N210" t="n">
         <v>225</v>
       </c>
-      <c r="O208" t="n">
+      <c r="O210" t="n">
         <v>225</v>
       </c>
-      <c r="R208" t="n">
+      <c r="R210" t="n">
         <v>0.06446335798731118</v>
       </c>
-      <c r="S208" t="inlineStr">
+      <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO208" t="inlineStr">
+      <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP208" t="inlineStr">
+      <c r="AP210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR208" t="inlineStr">
+      <c r="AR210" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS208" t="inlineStr"/>
-      <c r="AT208" t="n">
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="n">
         <v>0</v>
       </c>
-      <c r="AU208" t="inlineStr">
+      <c r="AU210" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV208" t="inlineStr">
+      <c r="AV210" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW208" t="inlineStr">
+      <c r="AW210" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX208" t="inlineStr">
+      <c r="AX210" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY208" t="inlineStr">
+      <c r="AY210" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ208" t="inlineStr">
+      <c r="AZ210" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA208" t="inlineStr">
+      <c r="BA210" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB208" t="inlineStr">
+      <c r="BB210" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC208" t="inlineStr">
+      <c r="BC210" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>4</v>
+      </c>
+      <c r="O211" t="n">
+        <v>4</v>
+      </c>
+      <c r="P211" t="n">
+        <v>4</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA211" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>4</v>
+      </c>
+      <c r="O212" t="n">
+        <v>4</v>
+      </c>
+      <c r="P212" t="n">
+        <v>4</v>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38285,7 +39077,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -38368,7 +39160,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -38378,7 +39170,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -38398,7 +39190,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -38430,7 +39222,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7829</v>
+        <v>7873</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -36010,13 +36010,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="O196" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="R196" t="n">
-        <v>0.4811383483570925</v>
+        <v>0.5178664665522904</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -39222,7 +39222,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7873</v>
+        <v>7883</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25627,7 +25627,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -35858,7 +35858,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -37871,7 +37871,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38959,7 +38959,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -39041,6 +39041,151 @@
       <c r="BC212" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>214</v>
+      </c>
+      <c r="O213" t="n">
+        <v>214</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.06131181604126484</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39222,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -39160,7 +39305,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
@@ -39170,7 +39315,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -39222,7 +39367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7883</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25627,7 +25627,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -35858,7 +35858,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -37871,7 +37871,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38959,7 +38959,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24533,7 +24533,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25627,7 +25627,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30738,7 +30738,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31282,7 +31282,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -35314,7 +35314,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -35858,7 +35858,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -37871,7 +37871,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -38959,7 +38959,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -32078,12 +32078,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -32117,13 +32117,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R175" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -32156,42 +32156,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32223,12 +32223,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -32262,95 +32262,81 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O176" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R176" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32363,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -32426,98 +32412,23 @@
       <c r="O177" t="n">
         <v>18</v>
       </c>
+      <c r="R177" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
-        <v>1</v>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
@@ -32611,17 +32522,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32655,22 +32566,39 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O178" t="n">
-        <v>10</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0.1891260466471829</v>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -32678,6 +32606,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN178" t="b">
+        <v>1</v>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -32695,7 +32681,7 @@
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -32708,42 +32694,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -32770,7 +32756,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -32819,98 +32805,23 @@
       <c r="O179" t="n">
         <v>10</v>
       </c>
+      <c r="R179" t="n">
+        <v>0.1891260466471829</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -33004,17 +32915,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33048,22 +32959,39 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="O180" t="n">
-        <v>76</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.7102109125495343</v>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -33071,6 +32999,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly shigellosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33088,7 +33074,7 @@
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+          <t>SER_NZ_SHIGELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -33101,42 +33087,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33163,7 +33149,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -33212,98 +33198,23 @@
       <c r="O181" t="n">
         <v>76</v>
       </c>
+      <c r="R181" t="n">
+        <v>0.7102109125495343</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Shigellainfektion</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -33397,17 +33308,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33441,22 +33352,39 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="O182" t="n">
-        <v>20</v>
-      </c>
-      <c r="R182" t="n">
-        <v>0.08691384892873792</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>76</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Shigellainfektion</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -33464,9 +33392,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN182" t="b">
+        <v>1</v>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
@@ -33476,12 +33462,12 @@
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -33489,47 +33475,47 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -33556,7 +33542,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -33605,98 +33591,23 @@
       <c r="O183" t="n">
         <v>20</v>
       </c>
+      <c r="R183" t="n">
+        <v>0.08691384892873792</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -33790,17 +33701,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -33825,7 +33736,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -33834,81 +33745,170 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="O184" t="n">
-        <v>136</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.03896451860566364</v>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33940,12 +33940,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -33970,7 +33970,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -33979,98 +33979,81 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="O185" t="n">
-        <v>1</v>
-      </c>
-      <c r="P185" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="R185" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.03896451860566364</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34097,7 +34080,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -34149,98 +34132,23 @@
       <c r="P186" t="n">
         <v>1</v>
       </c>
+      <c r="R186" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U186" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN186" t="b">
-        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
@@ -34334,17 +34242,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -34369,7 +34277,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -34378,81 +34286,173 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="O187" t="n">
-        <v>165</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.04727312919069485</v>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P187" t="n">
+        <v>1</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN187" t="b">
+        <v>1</v>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34484,12 +34484,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34523,98 +34523,81 @@
         </is>
       </c>
       <c r="N188" t="n">
+        <v>165</v>
+      </c>
+      <c r="O188" t="n">
+        <v>165</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.04727312919069485</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
         <v>0</v>
       </c>
-      <c r="O188" t="n">
-        <v>0</v>
-      </c>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP188" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT188" t="n">
-        <v>1</v>
-      </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -34641,7 +34624,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -34693,98 +34676,23 @@
       <c r="P189" t="n">
         <v>0</v>
       </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN189" t="b">
-        <v>1</v>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
@@ -34878,17 +34786,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34913,7 +34821,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -34922,81 +34830,173 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>224</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0.06417685417403424</v>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN190" t="b">
+        <v>1</v>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35028,12 +35028,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -35067,98 +35067,81 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
-      </c>
-      <c r="P191" t="n">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="R191" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.06417685417403424</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35185,7 +35168,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -35237,98 +35220,23 @@
       <c r="P192" t="n">
         <v>1</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -35422,17 +35330,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -35457,7 +35365,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -35466,81 +35374,173 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>234</v>
+        <v>1</v>
       </c>
       <c r="O193" t="n">
-        <v>234</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.06704189230680362</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35572,12 +35572,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -35602,7 +35602,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -35611,98 +35611,81 @@
         </is>
       </c>
       <c r="N194" t="n">
+        <v>234</v>
+      </c>
+      <c r="O194" t="n">
+        <v>234</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.06704189230680362</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
         <v>0</v>
       </c>
-      <c r="O194" t="n">
-        <v>0</v>
-      </c>
-      <c r="P194" t="n">
-        <v>0</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT194" t="n">
-        <v>1</v>
-      </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35729,7 +35712,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -35781,98 +35764,23 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -35966,17 +35874,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -36001,90 +35909,182 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>141</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.5178664665522904</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36116,12 +36116,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -36155,95 +36155,81 @@
         </is>
       </c>
       <c r="N197" t="n">
+        <v>151</v>
+      </c>
+      <c r="O197" t="n">
+        <v>151</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0.5545945847474882</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
         <v>0</v>
       </c>
-      <c r="O197" t="n">
-        <v>0</v>
-      </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="AT197" t="n">
-        <v>1</v>
-      </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36270,7 +36256,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -36319,98 +36305,23 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="R198" t="n">
+        <v>0</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1210</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>Shigella</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN198" t="b">
-        <v>1</v>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
@@ -36504,17 +36415,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -36548,81 +36459,170 @@
         </is>
       </c>
       <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Shigella</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1210.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
         <v>1</v>
       </c>
-      <c r="O199" t="n">
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1210</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
         <v>1</v>
       </c>
-      <c r="R199" t="n">
-        <v>0.001937969923792046</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
-      <c r="AT199" t="n">
-        <v>0</v>
-      </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -36654,12 +36654,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -36693,95 +36693,81 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O200" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R200" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -36808,7 +36794,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -36857,98 +36843,23 @@
       <c r="O201" t="n">
         <v>7</v>
       </c>
+      <c r="R201" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_502_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Shigellose</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -37042,17 +36953,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -37086,22 +36997,39 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O202" t="n">
-        <v>4</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_502_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Shigellose</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -37109,9 +37037,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
@@ -37121,12 +37107,12 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -37134,47 +37120,47 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37201,7 +37187,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -37250,98 +37236,23 @@
       <c r="O203" t="n">
         <v>4</v>
       </c>
+      <c r="R203" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
@@ -37435,17 +37346,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -37479,81 +37390,170 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="O204" t="n">
-        <v>226</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.0647498618005881</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37585,12 +37585,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -37615,7 +37615,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -37624,98 +37624,81 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
-      </c>
-      <c r="P205" t="n">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="R205" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37742,7 +37725,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -37794,98 +37777,23 @@
       <c r="P206" t="n">
         <v>1</v>
       </c>
+      <c r="R206" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -37979,17 +37887,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -38014,7 +37922,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -38023,81 +37931,173 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>232</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>232</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0.06646888468024974</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1</v>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>1</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38129,12 +38129,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -38159,7 +38159,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -38168,98 +38168,81 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="O208" t="n">
-        <v>1</v>
-      </c>
-      <c r="P208" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="R208" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.06646888468024974</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38286,7 +38269,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -38338,98 +38321,23 @@
       <c r="P209" t="n">
         <v>1</v>
       </c>
+      <c r="R209" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U209" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -38523,17 +38431,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -38558,7 +38466,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -38567,81 +38475,173 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>225</v>
+        <v>1</v>
       </c>
       <c r="O210" t="n">
-        <v>225</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.06446335798731118</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P210" t="n">
+        <v>1</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38673,12 +38673,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -38712,98 +38712,81 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="O211" t="n">
-        <v>4</v>
-      </c>
-      <c r="P211" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="R211" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.06446335798731118</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38830,7 +38813,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -38882,98 +38865,23 @@
       <c r="P212" t="n">
         <v>4</v>
       </c>
+      <c r="R212" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Bacterial dysentery</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -39067,123 +38975,360 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="n">
+        <v>4</v>
+      </c>
+      <c r="P213" t="n">
+        <v>4</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Bacterial dysentery</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Japan NIID bacterial dysentery (shigellosis) notifications.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_JP_SHIGELLOSIS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>shigellosis</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>D105</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Shigellosis</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>志贺菌病</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N213" t="n">
+      <c r="N214" t="n">
         <v>214</v>
       </c>
-      <c r="O213" t="n">
+      <c r="O214" t="n">
         <v>214</v>
       </c>
-      <c r="R213" t="n">
+      <c r="R214" t="n">
         <v>0.06131181604126484</v>
       </c>
-      <c r="S213" t="inlineStr">
+      <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO213" t="inlineStr">
+      <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP213" t="inlineStr">
+      <c r="AP214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR213" t="inlineStr">
+      <c r="AR214" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS213" t="inlineStr"/>
-      <c r="AT213" t="n">
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="n">
         <v>0</v>
       </c>
-      <c r="AU213" t="inlineStr">
+      <c r="AU214" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV213" t="inlineStr">
+      <c r="AV214" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW213" t="inlineStr">
+      <c r="AW214" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX213" t="inlineStr">
+      <c r="AX214" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY213" t="inlineStr">
+      <c r="AY214" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ213" t="inlineStr">
+      <c r="AZ214" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA213" t="inlineStr">
+      <c r="BA214" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB213" t="inlineStr">
+      <c r="BB214" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC213" t="inlineStr">
+      <c r="BC214" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -39305,7 +39450,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -39315,7 +39460,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -39367,7 +39512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8097</v>
+        <v>8108</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2164,17 +2174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2398,17 +2413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2945,7 +2965,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2953,17 +2973,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3179,7 +3204,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3187,17 +3212,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3865,7 +3895,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4412,7 +4442,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4959,7 +4989,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5506,7 +5536,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6519,7 +6549,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -6527,17 +6557,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -6753,7 +6788,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6761,17 +6796,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7274,7 +7314,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -7601,7 +7641,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -7609,17 +7649,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -7835,7 +7880,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -7843,17 +7888,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8390,7 +8440,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8398,17 +8448,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8624,7 +8679,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8632,17 +8687,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9310,7 +9370,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9857,7 +9917,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -10404,7 +10464,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11417,7 +11477,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -11425,17 +11485,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -11651,7 +11716,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11659,17 +11724,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12172,7 +12242,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -12499,7 +12569,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -12507,17 +12577,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -12733,7 +12808,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -12741,17 +12816,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13288,7 +13368,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -13296,17 +13376,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -13522,7 +13607,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -13530,17 +13615,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14208,7 +14298,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -14755,7 +14845,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15302,7 +15392,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15849,7 +15939,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16711,7 +16801,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -16719,17 +16809,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -16945,7 +17040,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -16953,17 +17048,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -17394,7 +17494,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -17402,17 +17502,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -17628,7 +17733,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -17636,17 +17741,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -18180,7 +18290,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -18188,17 +18298,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -18414,7 +18529,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -18422,17 +18537,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19097,7 +19217,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -19644,7 +19764,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -20191,7 +20311,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20738,7 +20858,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21600,7 +21720,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -21608,17 +21728,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -21834,7 +21959,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -21842,17 +21967,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -22283,7 +22413,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -22291,17 +22421,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -22517,7 +22652,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -22525,17 +22660,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -23069,7 +23209,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
@@ -23077,17 +23217,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS125" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -23303,7 +23448,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -23311,17 +23456,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -23986,7 +24136,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -24533,7 +24683,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25080,7 +25230,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25627,7 +25777,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -26171,7 +26321,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27033,7 +27183,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
@@ -27041,17 +27191,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS147" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -27267,7 +27422,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
@@ -27275,17 +27430,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS148" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -27716,7 +27876,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -27724,17 +27884,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS151" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -27950,7 +28115,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -27958,17 +28123,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS152" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -28502,7 +28672,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -28510,17 +28680,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS155" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -28736,7 +28911,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -28744,17 +28919,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS156" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -29650,7 +29830,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -30194,7 +30374,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30738,7 +30918,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -31282,7 +31462,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -31754,7 +31934,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
@@ -31762,17 +31942,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS173" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -31988,7 +32173,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
@@ -31996,17 +32181,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS174" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -32437,7 +32627,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -32445,17 +32635,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS177" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -32671,7 +32866,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -32679,17 +32874,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS178" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -33223,7 +33423,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -33231,17 +33431,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -33457,7 +33662,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -33465,17 +33670,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS182" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_SHIGELLA</t>
         </is>
       </c>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -34371,7 +34581,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -34915,7 +35125,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -35459,7 +35669,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -36003,7 +36213,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -36155,13 +36365,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="O197" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="R197" t="n">
-        <v>0.5545945847474882</v>
+        <v>0.5803042674841269</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -36330,7 +36540,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
@@ -36338,17 +36548,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS198" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -36564,7 +36779,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -36572,17 +36787,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1210</t>
         </is>
       </c>
       <c r="AT199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -36868,7 +37088,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -36876,17 +37096,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -37102,7 +37327,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -37110,17 +37335,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS202" t="inlineStr">
         <is>
           <t>SER_NO_FHI_502_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -38016,7 +38246,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -38560,7 +38790,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -39104,7 +39334,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -39512,7 +39742,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8108</v>
+        <v>8115</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d105/2026-2029.xlsx
+++ b/diseases/d105/2026-2029.xlsx
@@ -38069,13 +38069,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O209" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R209" t="n">
-        <v>0.6941614338892403</v>
+        <v>0.7015070575282799</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
@@ -39066,13 +39066,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -39230,10 +39230,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -42731,13 +42731,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O236" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R236" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8902</v>
+        <v>8908</v>
       </c>
     </row>
     <row r="16">
